--- a/fsh/ig/cm-v3-administrative-gender.xlsx
+++ b/fsh/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T07:31:01+00:00</t>
+    <t>2026-04-13T09:05:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fsh/ig/cm-v3-administrative-gender.xlsx
+++ b/fsh/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:05:14+00:00</t>
+    <t>2026-04-13T09:40:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fsh/ig/cm-v3-administrative-gender.xlsx
+++ b/fsh/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:40:13+00:00</t>
+    <t>2026-04-13T09:48:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fsh/ig/cm-v3-administrative-gender.xlsx
+++ b/fsh/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:48:02+00:00</t>
+    <t>2026-04-13T09:58:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fsh/ig/cm-v3-administrative-gender.xlsx
+++ b/fsh/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:58:36+00:00</t>
+    <t>2026-04-13T12:10:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
